--- a/Sample_run/1/student/DuyCNHE187327/TC6/GradeDetail.xlsx
+++ b/Sample_run/1/student/DuyCNHE187327/TC6/GradeDetail.xlsx
@@ -215,6 +215,12 @@
     <x:t>{"StudentId":"S111","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
   </x:si>
   <x:si>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
+  </x:si>
+  <x:si>
     <x:t>(Not validated by this test case)</x:t>
   </x:si>
   <x:si>
@@ -222,6 +228,9 @@
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIN, PSH, ACK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -248,7 +257,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -263,6 +272,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFF00"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -290,7 +304,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -306,8 +320,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -325,6 +342,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -984,7 +1005,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R26"/>
+  <x:dimension ref="A1:R25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -997,7 +1018,7 @@
     <x:col min="8" max="8" width="143.853482" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
@@ -1110,7 +1131,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35908</x:v>
+        <x:v>45408</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1169,7 +1190,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>35908</x:v>
+        <x:v>45408</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1222,7 +1243,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35908</x:v>
+        <x:v>45408</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1278,7 +1299,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35908</x:v>
+        <x:v>45408</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1337,7 +1358,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35908</x:v>
+        <x:v>45408</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>48</x:v>
@@ -1393,7 +1414,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>35908</x:v>
+        <x:v>45408</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>58</x:v>
@@ -1446,7 +1467,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>35908</x:v>
+        <x:v>45408</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1505,7 +1526,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>35908</x:v>
+        <x:v>45408</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>58</x:v>
@@ -1558,7 +1579,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>35908</x:v>
+        <x:v>45408</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1614,7 +1635,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>35908</x:v>
+        <x:v>45408</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1673,7 +1694,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q12" s="0">
-        <x:v>35908</x:v>
+        <x:v>45408</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
         <x:v>58</x:v>
@@ -1726,7 +1747,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>54194</x:v>
+        <x:v>41702</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1785,7 +1806,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>54194</x:v>
+        <x:v>41702</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1838,7 +1859,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>54194</x:v>
+        <x:v>41702</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1894,7 +1915,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>54194</x:v>
+        <x:v>41702</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1953,7 +1974,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>54194</x:v>
+        <x:v>41702</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>48</x:v>
@@ -2009,7 +2030,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q18" s="0">
-        <x:v>54194</x:v>
+        <x:v>41702</x:v>
       </x:c>
       <x:c r="R18" s="3" t="s">
         <x:v>58</x:v>
@@ -2062,7 +2083,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>54194</x:v>
+        <x:v>41702</x:v>
       </x:c>
       <x:c r="Q19" s="0">
         <x:v>4000</x:v>
@@ -2106,25 +2127,25 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="L20" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="M20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N20" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O20" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P20" s="0">
+        <x:v>41702</x:v>
+      </x:c>
+      <x:c r="Q20" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="Q20" s="0">
-        <x:v>54194</x:v>
-      </x:c>
-      <x:c r="R20" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="R20" s="2" t="s">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2174,7 +2195,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
-        <x:v>54194</x:v>
+        <x:v>41702</x:v>
       </x:c>
       <x:c r="Q21" s="0">
         <x:v>4000</x:v>
@@ -2215,28 +2236,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N22" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P22" s="0">
-        <x:v>54194</x:v>
-      </x:c>
-      <x:c r="Q22" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R22" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R22" s="4" t="s">
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2277,22 +2298,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M23" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N23" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P23" s="0">
-        <x:v>54194</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q23" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R23" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>41702</x:v>
+      </x:c>
+      <x:c r="R23" s="3" t="s">
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:18">
@@ -2300,7 +2321,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>17</x:v>
@@ -2339,16 +2360,16 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="O24" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="P24" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q24" s="0">
-        <x:v>35908</x:v>
-      </x:c>
-      <x:c r="R24" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>45408</x:v>
+      </x:c>
+      <x:c r="R24" s="5" t="s">
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:18">
@@ -2356,7 +2377,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>17</x:v>
@@ -2383,10 +2404,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K25" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L25" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="M25" s="0" t="s">
         <x:v>47</x:v>
@@ -2395,72 +2416,16 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="O25" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="P25" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q25" s="0">
-        <x:v>54194</x:v>
-      </x:c>
-      <x:c r="R25" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:18">
-      <x:c r="A26" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K26" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="L26" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="M26" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N26" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O26" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P26" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q26" s="0">
-        <x:v>54194</x:v>
-      </x:c>
-      <x:c r="R26" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>41702</x:v>
+      </x:c>
+      <x:c r="R25" s="5" t="s">
+        <x:v>69</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
